--- a/Documentation/Best For Lists/Best Pets for Seniors with Dementia List.xlsx
+++ b/Documentation/Best For Lists/Best Pets for Seniors with Dementia List.xlsx
@@ -620,7 +620,7 @@
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated: 2026-07-12  |  Products shown: 16  |  Eliminated by dedup rule: 13</t>
+          <t>Generated: 2026-07-15  |  Products shown: 16  |  Eliminated by dedup rule: 13</t>
         </is>
       </c>
     </row>

--- a/Documentation/Best For Lists/Best Pets for Seniors with Dementia List.xlsx
+++ b/Documentation/Best For Lists/Best Pets for Seniors with Dementia List.xlsx
@@ -1462,22 +1462,20 @@
       </c>
       <c r="D16" s="12" t="inlineStr">
         <is>
-          <t>Budget Friendly</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="E16" s="12" t="inlineStr">
         <is>
-          <t>Dog</t>
-        </is>
-      </c>
-      <c r="F16" s="12" t="n">
-        <v>25.99</v>
-      </c>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F16" s="12" t="n"/>
       <c r="G16" s="12" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H16" s="12" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="I16" s="14" t="n">
         <v>3.1</v>

--- a/Documentation/Best For Lists/Best Pets for Seniors with Dementia List.xlsx
+++ b/Documentation/Best For Lists/Best Pets for Seniors with Dementia List.xlsx
@@ -620,7 +620,7 @@
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated: 2026-07-15  |  Products shown: 16  |  Eliminated by dedup rule: 13</t>
+          <t>Generated: 2026-07-16  |  Products shown: 16  |  Eliminated by dedup rule: 13</t>
         </is>
       </c>
     </row>

--- a/Documentation/Best For Lists/Best Pets for Seniors with Dementia List.xlsx
+++ b/Documentation/Best For Lists/Best Pets for Seniors with Dementia List.xlsx
@@ -620,7 +620,7 @@
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated: 2026-07-16  |  Products shown: 16  |  Eliminated by dedup rule: 13</t>
+          <t>Generated: 2026-08-10  |  Products shown: 16  |  Eliminated by dedup rule: 13</t>
         </is>
       </c>
     </row>
@@ -786,7 +786,7 @@
         <v>4.5</v>
       </c>
       <c r="H5" s="8" t="n">
-        <v>11640</v>
+        <v>12310</v>
       </c>
       <c r="I5" s="9" t="n">
         <v>4.7</v>
@@ -849,7 +849,7 @@
         <v>4.3</v>
       </c>
       <c r="H6" s="12" t="n">
-        <v>5164</v>
+        <v>5195</v>
       </c>
       <c r="I6" s="13" t="n">
         <v>4.7</v>
@@ -906,13 +906,13 @@
         </is>
       </c>
       <c r="F7" s="8" t="n">
-        <v>89</v>
+        <v>99</v>
       </c>
       <c r="G7" s="8" t="n">
         <v>5</v>
       </c>
       <c r="H7" s="8" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="I7" s="9" t="n">
         <v>4.35</v>
@@ -1032,13 +1032,13 @@
         </is>
       </c>
       <c r="F9" s="8" t="n">
-        <v>89</v>
+        <v>99</v>
       </c>
       <c r="G9" s="8" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="H9" s="8" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="I9" s="9" t="n">
         <v>4.35</v>
@@ -1081,7 +1081,7 @@
       </c>
       <c r="C10" s="11" t="inlineStr">
         <is>
-          <t>Grey Tabby Cat</t>
+          <t>Original Border Collie</t>
         </is>
       </c>
       <c r="D10" s="12" t="inlineStr">
@@ -1091,17 +1091,17 @@
       </c>
       <c r="E10" s="12" t="inlineStr">
         <is>
-          <t>Cat</t>
+          <t>Dog</t>
         </is>
       </c>
       <c r="F10" s="12" t="n">
         <v>44.45</v>
       </c>
       <c r="G10" s="12" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="H10" s="12" t="n">
-        <v>848</v>
+        <v>441</v>
       </c>
       <c r="I10" s="14" t="n">
         <v>3.8</v>
@@ -1129,7 +1129,7 @@
       </c>
       <c r="Q10" s="11" t="inlineStr">
         <is>
-          <t>Breathing-only mechanism; no sensors, voice, or touch response. Sound Level Control=1 — no on/off switch or mute (battery must be removed to silence). Autonomous Interaction=3: breathing runs continuously without user direction. Review strength estimated; recommend manual verification. Previously scored as 'Calico Cat' — now matched to 'Grey Tabby Cat' per repo. Verify this is the correct product match before publishing. Review Strength=4: 848 reviews, 4.3★ (repo data, 2026-06-22). SOUND QUALITY UPDATE (2026-07-01, Tim-confirmed): Perfect Petzzz is NOT silent — manufacturer FAQ confirms the breathing mechanism emits sound as normal operation, and multiple Amazon reviews describe a mechanical/grinding noise rather than a soothing breath. Sound Quality rescored from 2 to 2 under the new merged rubric (was previously scored under 'absence of sound = neutral' logic, now scored on actual sound character; net score unchanged at 2, but rationale corrected). Sound appears to vary unit to unit per manufacturer's own FAQ and mixed review reports (some units near-silent/subtle snore, others audibly grinding) — no per-unit review data available to differentiate individual SKUs, so all 8 Perfect Petzzz products scored uniformly at 2 pending any future unit-specific verification. DEMENTIA SUITABILITY EVIDENCE TIER (2026-07-02): Tier D — no dementia-specific evidence found (independent or manufacturer); score reflects general sub-criteria judgment only (simplicity, familiar form, calmness, safety). Capped at 3. Score is provisional pending dementia consultant review. DEMENTIA SUITABILITY RECALCULATED (2026-07-02, Tim-directed methodology): Simplicity=5, Familiar Form=4, Safety=5, Calmness=avg(Sound=2, Behavioral Realism=1)=1.5. Raw average of 4 sub-criteria=3.88, rounded=4, Evidence Tier D cap=3 -&gt; Final=3 (no change). This is a first-pass 'best effort' score pending dementia care consultant review (consultant search in progress as of 2026-07-02). Products in the 'Ai &amp; Robotic Pets' Type category are excluded from memory-care-relevant Best For lists via a separate Type filter in the Best For Weighting Table, independent of this score.</t>
+          <t>Breathing-only mechanism; no sensors, voice, or touch response. Sound Level Control=1 — no on/off switch or mute (battery must be removed to silence). Autonomous Interaction=3: breathing runs continuously without user direction. Review strength estimated; recommend manual verification. Product name updated: 'Original Border Collie' per repo. Review Strength=3: 403 reviews, 4.3★ (repo, 2026-06-22). SOUND QUALITY UPDATE (2026-07-01, Tim-confirmed): Perfect Petzzz is NOT silent — manufacturer FAQ confirms the breathing mechanism emits sound as normal operation, and multiple Amazon reviews describe a mechanical/grinding noise rather than a soothing breath. Sound Quality rescored from 2 to 2 under the new merged rubric (was previously scored under 'absence of sound = neutral' logic, now scored on actual sound character; net score unchanged at 2, but rationale corrected). Sound appears to vary unit to unit per manufacturer's own FAQ and mixed review reports (some units near-silent/subtle snore, others audibly grinding) — no per-unit review data available to differentiate individual SKUs, so all 8 Perfect Petzzz products scored uniformly at 2 pending any future unit-specific verification. DEMENTIA SUITABILITY EVIDENCE TIER (2026-07-02): Tier D — no dementia-specific evidence found (independent or manufacturer); score reflects general sub-criteria judgment only (simplicity, familiar form, calmness, safety). Capped at 3. Score is provisional pending dementia consultant review. DEMENTIA SUITABILITY RECALCULATED (2026-07-02, Tim-directed methodology): Simplicity=5, Familiar Form=4, Safety=5, Calmness=avg(Sound=2, Behavioral Realism=1)=1.5. Raw average of 4 sub-criteria=3.88, rounded=4, Evidence Tier D cap=3 -&gt; Final=3 (no change). This is a first-pass 'best effort' score pending dementia care consultant review (consultant search in progress as of 2026-07-02). Products in the 'Ai &amp; Robotic Pets' Type category are excluded from memory-care-relevant Best For lists via a separate Type filter in the Best For Weighting Table, independent of this score.</t>
         </is>
       </c>
     </row>
@@ -1144,7 +1144,7 @@
       </c>
       <c r="C11" s="7" t="inlineStr">
         <is>
-          <t>Original Chocolate Lab</t>
+          <t>Original Plush White Cat</t>
         </is>
       </c>
       <c r="D11" s="8" t="inlineStr">
@@ -1154,17 +1154,17 @@
       </c>
       <c r="E11" s="8" t="inlineStr">
         <is>
-          <t>Dog</t>
+          <t>Cat</t>
         </is>
       </c>
       <c r="F11" s="8" t="n">
-        <v>44.45</v>
+        <v>53.9</v>
       </c>
       <c r="G11" s="8" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="H11" s="8" t="n">
-        <v>553</v>
+        <v>55</v>
       </c>
       <c r="I11" s="15" t="n">
         <v>3.8</v>
@@ -1192,7 +1192,7 @@
       </c>
       <c r="Q11" s="7" t="inlineStr">
         <is>
-          <t>Breathing-only mechanism; no sensors, voice, or touch response. Sound Level Control=1 — no on/off switch or mute (battery must be removed to silence). Autonomous Interaction=3: breathing runs continuously without user direction. Review strength estimated; recommend manual verification. Product name updated: 'Original Chocolate Lab' per repo. Review Strength=4: 553 reviews, 4.3★ (repo, 2026-06-22). SOUND QUALITY UPDATE (2026-07-01, Tim-confirmed): Perfect Petzzz is NOT silent — manufacturer FAQ confirms the breathing mechanism emits sound as normal operation, and multiple Amazon reviews describe a mechanical/grinding noise rather than a soothing breath. Sound Quality rescored from 2 to 2 under the new merged rubric (was previously scored under 'absence of sound = neutral' logic, now scored on actual sound character; net score unchanged at 2, but rationale corrected). Sound appears to vary unit to unit per manufacturer's own FAQ and mixed review reports (some units near-silent/subtle snore, others audibly grinding) — no per-unit review data available to differentiate individual SKUs, so all 8 Perfect Petzzz products scored uniformly at 2 pending any future unit-specific verification. DEMENTIA SUITABILITY EVIDENCE TIER (2026-07-02): Tier D — no dementia-specific evidence found (independent or manufacturer); score reflects general sub-criteria judgment only (simplicity, familiar form, calmness, safety). Capped at 3. Score is provisional pending dementia consultant review. DEMENTIA SUITABILITY RECALCULATED (2026-07-02, Tim-directed methodology): Simplicity=5, Familiar Form=4, Safety=5, Calmness=avg(Sound=2, Behavioral Realism=1)=1.5. Raw average of 4 sub-criteria=3.88, rounded=4, Evidence Tier D cap=3 -&gt; Final=3 (no change). This is a first-pass 'best effort' score pending dementia care consultant review (consultant search in progress as of 2026-07-02). Products in the 'Ai &amp; Robotic Pets' Type category are excluded from memory-care-relevant Best For lists via a separate Type filter in the Best For Weighting Table, independent of this score.</t>
+          <t>Breathing-only mechanism; no sensors, voice, or touch response. Sound Level Control=1 — no on/off switch or mute (battery must be removed to silence). Autonomous Interaction=3: breathing runs continuously without user direction. Review strength estimated; recommend manual verification. White coat: higher visual contrast against most furniture/bedding. Product name updated: 'Original Plush White Cat' per repo. Review Strength=2: 54 reviews, 4.0★ (repo, 2026-06-22). SOUND QUALITY UPDATE (2026-07-01, Tim-confirmed): Perfect Petzzz is NOT silent — manufacturer FAQ confirms the breathing mechanism emits sound as normal operation, and multiple Amazon reviews describe a mechanical/grinding noise rather than a soothing breath. Sound Quality rescored from 2 to 2 under the new merged rubric (was previously scored under 'absence of sound = neutral' logic, now scored on actual sound character; net score unchanged at 2, but rationale corrected). Sound appears to vary unit to unit per manufacturer's own FAQ and mixed review reports (some units near-silent/subtle snore, others audibly grinding) — no per-unit review data available to differentiate individual SKUs, so all 8 Perfect Petzzz products scored uniformly at 2 pending any future unit-specific verification. DEMENTIA SUITABILITY EVIDENCE TIER (2026-07-02): Tier D — no dementia-specific evidence found (independent or manufacturer); score reflects general sub-criteria judgment only (simplicity, familiar form, calmness, safety). Capped at 3. Score is provisional pending dementia consultant review. DEMENTIA SUITABILITY RECALCULATED (2026-07-02, Tim-directed methodology): Simplicity=5, Familiar Form=4, Safety=5, Calmness=avg(Sound=2, Behavioral Realism=1)=1.5. Raw average of 4 sub-criteria=3.88, rounded=4, Evidence Tier D cap=3 -&gt; Final=3 (no change). This is a first-pass 'best effort' score pending dementia care consultant review (consultant search in progress as of 2026-07-02). Products in the 'Ai &amp; Robotic Pets' Type category are excluded from memory-care-relevant Best For lists via a separate Type filter in the Best For Weighting Table, independent of this score.</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
         </is>
       </c>
       <c r="F13" s="8" t="n">
-        <v>119</v>
+        <v>139</v>
       </c>
       <c r="G13" s="8" t="n">
         <v>5</v>
@@ -1345,13 +1345,13 @@
         </is>
       </c>
       <c r="F14" s="12" t="n">
-        <v>50.11</v>
+        <v>69.98999999999999</v>
       </c>
       <c r="G14" s="12" t="n">
         <v>4.8</v>
       </c>
       <c r="H14" s="12" t="n">
-        <v>772</v>
+        <v>1132</v>
       </c>
       <c r="I14" s="14" t="n">
         <v>3.5</v>
@@ -1411,10 +1411,10 @@
         <v>349</v>
       </c>
       <c r="G15" s="8" t="n">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="H15" s="8" t="n">
-        <v>17</v>
+        <v>47</v>
       </c>
       <c r="I15" s="15" t="n">
         <v>3.25</v>
@@ -1535,10 +1535,10 @@
         <v>69.98999999999999</v>
       </c>
       <c r="G17" s="8" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="H17" s="8" t="n">
-        <v>283</v>
+        <v>346</v>
       </c>
       <c r="I17" s="16" t="n">
         <v>2.85</v>
@@ -1598,10 +1598,10 @@
         <v>499</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="H18" s="12" t="n">
-        <v>1199</v>
+        <v>1231</v>
       </c>
       <c r="I18" s="17" t="n">
         <v>1.95</v>
@@ -1644,12 +1644,12 @@
       </c>
       <c r="C19" s="7" t="inlineStr">
         <is>
-          <t>ROLA Mini Pet Monitor</t>
+          <t>EBO Air 2 Plus FamilyBot</t>
         </is>
       </c>
       <c r="D19" s="8" t="inlineStr">
         <is>
-          <t>Best Value</t>
+          <t>Premium</t>
         </is>
       </c>
       <c r="E19" s="8" t="inlineStr">
@@ -1658,13 +1658,13 @@
         </is>
       </c>
       <c r="F19" s="8" t="n">
-        <v>139</v>
+        <v>319</v>
       </c>
       <c r="G19" s="8" t="n">
         <v>5</v>
       </c>
       <c r="H19" s="8" t="n">
-        <v>73</v>
+        <v>42</v>
       </c>
       <c r="I19" s="16" t="n">
         <v>1.75</v>
@@ -1692,7 +1692,7 @@
       </c>
       <c r="Q19" s="7" t="inlineStr">
         <is>
-          <t>Camera=yes, Internet Access=yes per Product Matrix. Hard-shell rolling security camera robot; not a companion pet. Scores are category-level; minor spec differences between models noted. Review strength and Value estimated — recommend manual Amazon verification. ROLA Mini is the most compact Enabot; Size=5. Charging=4 (dock, but smaller form factor). Product renamed to 'ROLA Mini Pet Monitor'. Review Strength=3: 73 reviews, 5★ (repo data, 2026-06-22). DEMENTIA SUITABILITY EVIDENCE TIER (2026-07-02): Tier D — no dementia-specific evidence found (independent or manufacturer); score reflects general sub-criteria judgment only (simplicity, familiar form, calmness, safety). Capped at 3. Score is provisional pending dementia consultant review. DEMENTIA SUITABILITY RECALCULATED (2026-07-02, Tim-directed methodology): Simplicity=2, Familiar Form=1, Safety=2, Calmness=avg(Sound=3, Behavioral Realism=1)=2.0. Raw average of 4 sub-criteria=1.75, rounded=2, Evidence Tier D cap=3 -&gt; Final=2 (was 1). This is a first-pass 'best effort' score pending dementia care consultant review (consultant search in progress as of 2026-07-02). Products in the 'Ai &amp; Robotic Pets' Type category are excluded from memory-care-relevant Best For lists via a separate Type filter in the Best For Weighting Table, independent of this score.</t>
+          <t>Camera=yes, Internet Access=yes per Product Matrix. Hard-shell rolling security camera robot; not a companion pet. Scores are category-level; minor spec differences between models noted. Review strength and Value estimated — recommend manual Amazon verification. Air 2 Plus has AI chat mode — highest AI tier in Enabot lineup per manufacturer. Product renamed to 'EBO Air 2 Plus FamilyBot'. Review Strength=3: 42 reviews, 5★ (repo data, 2026-06-22). DEMENTIA SUITABILITY EVIDENCE TIER (2026-07-02): Tier D — no dementia-specific evidence found (independent or manufacturer); score reflects general sub-criteria judgment only (simplicity, familiar form, calmness, safety). Capped at 3. Score is provisional pending dementia consultant review. DEMENTIA SUITABILITY RECALCULATED (2026-07-02, Tim-directed methodology): Simplicity=2, Familiar Form=1, Safety=2, Calmness=avg(Sound=3, Behavioral Realism=1)=2.0. Raw average of 4 sub-criteria=1.75, rounded=2, Evidence Tier D cap=3 -&gt; Final=2 (was 1). This is a first-pass 'best effort' score pending dementia care consultant review (consultant search in progress as of 2026-07-02). Products in the 'Ai &amp; Robotic Pets' Type category are excluded from memory-care-relevant Best For lists via a separate Type filter in the Best For Weighting Table, independent of this score.</t>
         </is>
       </c>
     </row>
@@ -1707,12 +1707,12 @@
       </c>
       <c r="C20" s="11" t="inlineStr">
         <is>
-          <t>EBO Air 2 Plus FamilyBot</t>
+          <t>ROLA Mini Pet Monitor</t>
         </is>
       </c>
       <c r="D20" s="12" t="inlineStr">
         <is>
-          <t>Premium</t>
+          <t>Best Value</t>
         </is>
       </c>
       <c r="E20" s="12" t="inlineStr">
@@ -1721,13 +1721,13 @@
         </is>
       </c>
       <c r="F20" s="12" t="n">
-        <v>359</v>
+        <v>139</v>
       </c>
       <c r="G20" s="12" t="n">
         <v>5</v>
       </c>
       <c r="H20" s="12" t="n">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="I20" s="17" t="n">
         <v>1.75</v>
@@ -1755,7 +1755,7 @@
       </c>
       <c r="Q20" s="11" t="inlineStr">
         <is>
-          <t>Camera=yes, Internet Access=yes per Product Matrix. Hard-shell rolling security camera robot; not a companion pet. Scores are category-level; minor spec differences between models noted. Review strength and Value estimated — recommend manual Amazon verification. Air 2 Plus has AI chat mode — highest AI tier in Enabot lineup per manufacturer. Product renamed to 'EBO Air 2 Plus FamilyBot'. Review Strength=3: 42 reviews, 5★ (repo data, 2026-06-22). DEMENTIA SUITABILITY EVIDENCE TIER (2026-07-02): Tier D — no dementia-specific evidence found (independent or manufacturer); score reflects general sub-criteria judgment only (simplicity, familiar form, calmness, safety). Capped at 3. Score is provisional pending dementia consultant review. DEMENTIA SUITABILITY RECALCULATED (2026-07-02, Tim-directed methodology): Simplicity=2, Familiar Form=1, Safety=2, Calmness=avg(Sound=3, Behavioral Realism=1)=2.0. Raw average of 4 sub-criteria=1.75, rounded=2, Evidence Tier D cap=3 -&gt; Final=2 (was 1). This is a first-pass 'best effort' score pending dementia care consultant review (consultant search in progress as of 2026-07-02). Products in the 'Ai &amp; Robotic Pets' Type category are excluded from memory-care-relevant Best For lists via a separate Type filter in the Best For Weighting Table, independent of this score.</t>
+          <t>Camera=yes, Internet Access=yes per Product Matrix. Hard-shell rolling security camera robot; not a companion pet. Scores are category-level; minor spec differences between models noted. Review strength and Value estimated — recommend manual Amazon verification. ROLA Mini is the most compact Enabot; Size=5. Charging=4 (dock, but smaller form factor). Product renamed to 'ROLA Mini Pet Monitor'. Review Strength=3: 73 reviews, 5★ (repo data, 2026-06-22). DEMENTIA SUITABILITY EVIDENCE TIER (2026-07-02): Tier D — no dementia-specific evidence found (independent or manufacturer); score reflects general sub-criteria judgment only (simplicity, familiar form, calmness, safety). Capped at 3. Score is provisional pending dementia consultant review. DEMENTIA SUITABILITY RECALCULATED (2026-07-02, Tim-directed methodology): Simplicity=2, Familiar Form=1, Safety=2, Calmness=avg(Sound=3, Behavioral Realism=1)=2.0. Raw average of 4 sub-criteria=1.75, rounded=2, Evidence Tier D cap=3 -&gt; Final=2 (was 1). This is a first-pass 'best effort' score pending dementia care consultant review (consultant search in progress as of 2026-07-02). Products in the 'Ai &amp; Robotic Pets' Type category are excluded from memory-care-relevant Best For lists via a separate Type filter in the Best For Weighting Table, independent of this score.</t>
         </is>
       </c>
     </row>
@@ -1976,7 +1976,7 @@
         <v>4.35</v>
       </c>
       <c r="F6" s="20" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="G6" s="20" t="inlineStr">
         <is>
@@ -1985,7 +1985,7 @@
       </c>
       <c r="H6" s="20" t="inlineStr">
         <is>
-          <t>score=4.35 rating=4.6</t>
+          <t>score=4.35 rating=4.5</t>
         </is>
       </c>
     </row>
@@ -2014,7 +2014,7 @@
         <v>4.2</v>
       </c>
       <c r="F7" s="19" t="n">
-        <v>4</v>
+        <v>4.95</v>
       </c>
       <c r="G7" s="19" t="inlineStr">
         <is>
@@ -2023,7 +2023,7 @@
       </c>
       <c r="H7" s="19" t="inlineStr">
         <is>
-          <t>score=4.20 rating=4</t>
+          <t>score=4.20 rating=4.95</t>
         </is>
       </c>
     </row>
@@ -2035,7 +2035,7 @@
       </c>
       <c r="B8" s="20" t="inlineStr">
         <is>
-          <t>Original Siamese Cat</t>
+          <t>Grey Tabby Cat</t>
         </is>
       </c>
       <c r="C8" s="20" t="inlineStr">
@@ -2052,16 +2052,16 @@
         <v>3.8</v>
       </c>
       <c r="F8" s="20" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="G8" s="20" t="inlineStr">
         <is>
-          <t>Grey Tabby Cat</t>
+          <t>Original Plush White Cat</t>
         </is>
       </c>
       <c r="H8" s="20" t="inlineStr">
         <is>
-          <t>score=3.80 rating=4.1</t>
+          <t>score=3.80 rating=4.2</t>
         </is>
       </c>
     </row>
@@ -2073,7 +2073,7 @@
       </c>
       <c r="B9" s="19" t="inlineStr">
         <is>
-          <t>Original Plush White Cat</t>
+          <t>Original Siamese Cat</t>
         </is>
       </c>
       <c r="C9" s="19" t="inlineStr">
@@ -2090,16 +2090,16 @@
         <v>3.8</v>
       </c>
       <c r="F9" s="19" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="G9" s="19" t="inlineStr">
         <is>
-          <t>Grey Tabby Cat</t>
+          <t>Original Plush White Cat</t>
         </is>
       </c>
       <c r="H9" s="19" t="inlineStr">
         <is>
-          <t>score=3.80 rating=4</t>
+          <t>score=3.80 rating=4.1</t>
         </is>
       </c>
     </row>
@@ -2187,7 +2187,7 @@
       </c>
       <c r="B12" s="20" t="inlineStr">
         <is>
-          <t>Original Border Collie</t>
+          <t>Original Chocolate Lab</t>
         </is>
       </c>
       <c r="C12" s="20" t="inlineStr">
@@ -2208,7 +2208,7 @@
       </c>
       <c r="G12" s="20" t="inlineStr">
         <is>
-          <t>Original Chocolate Lab</t>
+          <t>Original Border Collie</t>
         </is>
       </c>
       <c r="H12" s="20" t="inlineStr">

--- a/Documentation/Best For Lists/Best Pets for Seniors with Dementia List.xlsx
+++ b/Documentation/Best For Lists/Best Pets for Seniors with Dementia List.xlsx
@@ -620,7 +620,7 @@
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated: 2026-08-10  |  Products shown: 16  |  Eliminated by dedup rule: 13</t>
+          <t>Generated: 2026-08-13  |  Products shown: 16  |  Eliminated by dedup rule: 13</t>
         </is>
       </c>
     </row>
